--- a/data/trans_orig/P6705-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6705-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo es desgastador emocionalmente en 2012</t>
+          <t>Población según si su trabajo es desgastador emocionalmente en 2012 (tasa de respuesta: 99,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54405</t>
+          <t>55346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40828</t>
+          <t>40547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63981</t>
+          <t>64023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78765</t>
+          <t>78802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>111940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>27790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>49236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37667</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>50986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78443</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>64483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t>37375</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>63306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94540</t>
+          <t>95059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49492</t>
+          <t>48881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37998</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60495</t>
+          <t>60866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171291</t>
+          <t>172323</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223777</t>
+          <t>224475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99906</t>
+          <t>98356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140756</t>
+          <t>138735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>282409</t>
+          <t>280808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349911</t>
+          <t>348989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116515</t>
+          <t>118725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162670</t>
+          <t>164691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81102</t>
+          <t>82051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119626</t>
+          <t>120414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207965</t>
+          <t>211356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267684</t>
+          <t>269382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230053</t>
+          <t>230060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285977</t>
+          <t>286525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133226</t>
+          <t>134493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175297</t>
+          <t>176641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372795</t>
+          <t>375762</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>446287</t>
+          <t>449934</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151123</t>
+          <t>148444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199463</t>
+          <t>199392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91334</t>
+          <t>91742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131252</t>
+          <t>127685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255052</t>
+          <t>256065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316449</t>
+          <t>314433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120719</t>
+          <t>117834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164484</t>
+          <t>163388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73210</t>
+          <t>74807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109813</t>
+          <t>110463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201803</t>
+          <t>204977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>260120</t>
+          <t>261356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24641</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28692</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54536</t>
+          <t>53112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59281</t>
+          <t>60751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93117</t>
+          <t>95281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>28930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>53289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>52088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82892</t>
+          <t>82473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84476</t>
+          <t>82843</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119929</t>
+          <t>118962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47032</t>
+          <t>48422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75537</t>
+          <t>75143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139405</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184977</t>
+          <t>182302</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60599</t>
+          <t>62520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94108</t>
+          <t>93678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61579</t>
+          <t>62227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>102964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146567</t>
+          <t>147651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49683</t>
+          <t>50189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79970</t>
+          <t>79847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44615</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73982</t>
+          <t>75127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102243</t>
+          <t>103763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144701</t>
+          <t>145325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244792</t>
+          <t>242900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>310082</t>
+          <t>307672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184965</t>
+          <t>184399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237972</t>
+          <t>237104</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>446108</t>
+          <t>446252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526164</t>
+          <t>525091</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189715</t>
+          <t>191302</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243502</t>
+          <t>244340</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133890</t>
+          <t>131682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181010</t>
+          <t>180619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>337032</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>407627</t>
+          <t>407760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>373892</t>
+          <t>375401</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>447740</t>
+          <t>446168</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>215087</t>
+          <t>214599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>269553</t>
+          <t>268355</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>606252</t>
+          <t>604292</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>691970</t>
+          <t>695048</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>242903</t>
+          <t>245402</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>308830</t>
+          <t>306956</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146331</t>
+          <t>146248</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>193182</t>
+          <t>196789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>405112</t>
+          <t>409565</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>486550</t>
+          <t>486870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>204786</t>
+          <t>202250</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>259735</t>
+          <t>258625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146278</t>
+          <t>147378</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>195283</t>
+          <t>195501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>364506</t>
+          <t>366832</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>442223</t>
+          <t>444794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo es desgastador emocionalmente en 2016</t>
+          <t>Población según si su trabajo es desgastador emocionalmente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>34256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57587</t>
+          <t>57212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>47906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>74749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39246</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>58783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34886</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58124</t>
+          <t>57764</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51766</t>
+          <t>51317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78403</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32304</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>20841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32038</t>
+          <t>31904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214031</t>
+          <t>215189</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270661</t>
+          <t>266935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123523</t>
+          <t>123088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164855</t>
+          <t>165979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348389</t>
+          <t>350745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421835</t>
+          <t>418980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154871</t>
+          <t>153408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202379</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117598</t>
+          <t>117213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158551</t>
+          <t>160079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284274</t>
+          <t>282560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>347293</t>
+          <t>345876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231981</t>
+          <t>229937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>291089</t>
+          <t>288127</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>159648</t>
+          <t>161135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>205372</t>
+          <t>206312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>405326</t>
+          <t>406731</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>477605</t>
+          <t>477887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139151</t>
+          <t>141519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185921</t>
+          <t>186573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96705</t>
+          <t>96056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134912</t>
+          <t>134406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245650</t>
+          <t>246807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308366</t>
+          <t>308189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69013</t>
+          <t>69722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107800</t>
+          <t>106684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57922</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90787</t>
+          <t>91983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136287</t>
+          <t>135616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186076</t>
+          <t>185385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57972</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88429</t>
+          <t>86811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89046</t>
+          <t>89233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>123670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166898</t>
+          <t>168511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>54376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82194</t>
+          <t>86475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63672</t>
+          <t>63167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96308</t>
+          <t>96373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138094</t>
+          <t>136522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>83629</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119134</t>
+          <t>119226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63426</t>
+          <t>63301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95181</t>
+          <t>94689</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157877</t>
+          <t>155314</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>205779</t>
+          <t>202195</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50805</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82484</t>
+          <t>82454</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>71258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103794</t>
+          <t>103034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143074</t>
+          <t>142513</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33417</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60123</t>
+          <t>60817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66250</t>
+          <t>67825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80230</t>
+          <t>80994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117646</t>
+          <t>117012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>326871</t>
+          <t>326038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>390894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205990</t>
+          <t>205107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>259804</t>
+          <t>260080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>545202</t>
+          <t>541774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>630698</t>
+          <t>630682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241389</t>
+          <t>242903</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>299739</t>
+          <t>302861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180515</t>
+          <t>181719</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>230112</t>
+          <t>232862</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>440964</t>
+          <t>438347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>518098</t>
+          <t>519736</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>373339</t>
+          <t>370476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>443221</t>
+          <t>439382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>252044</t>
+          <t>253179</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310625</t>
+          <t>309933</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>642565</t>
+          <t>643231</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>730524</t>
+          <t>731496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211561</t>
+          <t>212785</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>268237</t>
+          <t>268033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>158092</t>
+          <t>157907</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206969</t>
+          <t>208028</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>384443</t>
+          <t>384830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>456739</t>
+          <t>458538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122885</t>
+          <t>122521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171136</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110682</t>
+          <t>112331</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156129</t>
+          <t>156531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>244576</t>
+          <t>246885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310655</t>
+          <t>314267</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo es desgastador emocionalmente en 2023</t>
+          <t>Población según si su trabajo es desgastador emocionalmente en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16001</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>17462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,62 +7137,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4169</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139012</t>
+          <t>141962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>449396</t>
+          <t>459402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81610</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206584</t>
+          <t>207583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>600842</t>
+          <t>587591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111108</t>
+          <t>111085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>49424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35399</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144356</t>
+          <t>146716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162372</t>
+          <t>163030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89201</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>70419</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>244851</t>
+          <t>241851</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>82533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>107189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>37379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59358</t>
+          <t>60149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54572</t>
+          <t>53915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60454</t>
+          <t>60953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47217</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45626</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>47896</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74543</t>
+          <t>72615</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195076</t>
+          <t>195463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555413</t>
+          <t>552980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>93188</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121871</t>
+          <t>123304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>298983</t>
+          <t>299384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>747365</t>
+          <t>761884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29928</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137769</t>
+          <t>142476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47796</t>
+          <t>47039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>70512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>62942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>194969</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41737</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>197098</t>
+          <t>196030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96357</t>
+          <t>95994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126872</t>
+          <t>125218</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>108501</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>312864</t>
+          <t>311070</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95468</t>
+          <t>93688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60572</t>
+          <t>59266</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51210</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143454</t>
+          <t>143739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66484</t>
+          <t>66130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96487</t>
+          <t>99306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6705-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6705-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>53906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40547</t>
+          <t>39779</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64023</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78802</t>
+          <t>78952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111940</t>
+          <t>111790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27790</t>
+          <t>26431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>48136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37830</t>
+          <t>36921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>50798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79208</t>
+          <t>80380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>40463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64483</t>
+          <t>65930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37375</t>
+          <t>38575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95059</t>
+          <t>94895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>33497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,47 +1121,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>36443</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>25975</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>50160</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>15,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>36443</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>26376</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>48881</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18553</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>34703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60866</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172323</t>
+          <t>170709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>224475</t>
+          <t>226075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98356</t>
+          <t>100811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138735</t>
+          <t>140049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280808</t>
+          <t>286511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348989</t>
+          <t>351078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118725</t>
+          <t>120052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164691</t>
+          <t>165819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82051</t>
+          <t>80948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>118367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211356</t>
+          <t>210167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269382</t>
+          <t>270541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230060</t>
+          <t>230357</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>286525</t>
+          <t>289300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134493</t>
+          <t>131637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176641</t>
+          <t>176085</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375762</t>
+          <t>377314</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>449934</t>
+          <t>450114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148444</t>
+          <t>151196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199392</t>
+          <t>200627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91742</t>
+          <t>90778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127685</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256065</t>
+          <t>253960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314433</t>
+          <t>318430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117834</t>
+          <t>118691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163388</t>
+          <t>167061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74807</t>
+          <t>73491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110463</t>
+          <t>109514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>204977</t>
+          <t>205356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261356</t>
+          <t>264522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>52427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>59827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95281</t>
+          <t>95886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82473</t>
+          <t>84156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82843</t>
+          <t>82801</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118962</t>
+          <t>117742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75143</t>
+          <t>74739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>138580</t>
+          <t>139329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182302</t>
+          <t>185174</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93678</t>
+          <t>96392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62227</t>
+          <t>63399</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102964</t>
+          <t>103658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147651</t>
+          <t>147681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50189</t>
+          <t>48442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>79762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47280</t>
+          <t>45353</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75127</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103763</t>
+          <t>102997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145325</t>
+          <t>148072</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>242900</t>
+          <t>248781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>307672</t>
+          <t>309716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184399</t>
+          <t>182440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237104</t>
+          <t>235019</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>446252</t>
+          <t>445337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525091</t>
+          <t>529008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191302</t>
+          <t>189745</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244340</t>
+          <t>246540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131682</t>
+          <t>132134</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180619</t>
+          <t>179553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>337032</t>
+          <t>336599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>407760</t>
+          <t>407542</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>375401</t>
+          <t>373986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>446168</t>
+          <t>449769</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>214599</t>
+          <t>214703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>268355</t>
+          <t>273697</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>604292</t>
+          <t>607394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>695048</t>
+          <t>699772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>245402</t>
+          <t>247100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>306956</t>
+          <t>309938</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146248</t>
+          <t>145410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196789</t>
+          <t>194200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>409565</t>
+          <t>405987</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>486870</t>
+          <t>486165</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>202250</t>
+          <t>206015</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>258625</t>
+          <t>261849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147378</t>
+          <t>146727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>195501</t>
+          <t>196753</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366832</t>
+          <t>364570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>444794</t>
+          <t>441264</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47906</t>
+          <t>49147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74749</t>
+          <t>76997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>37455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58783</t>
+          <t>58063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>78472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32928</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215189</t>
+          <t>214849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266935</t>
+          <t>271145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123088</t>
+          <t>123101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165979</t>
+          <t>162882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350745</t>
+          <t>349531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418980</t>
+          <t>416061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153408</t>
+          <t>152290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201134</t>
+          <t>200365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117213</t>
+          <t>117624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160079</t>
+          <t>158709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282560</t>
+          <t>285540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>345876</t>
+          <t>346546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229937</t>
+          <t>232898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288127</t>
+          <t>290231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>162454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206312</t>
+          <t>206846</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>406731</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>477887</t>
+          <t>478701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141519</t>
+          <t>140136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186573</t>
+          <t>186390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96056</t>
+          <t>94110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134406</t>
+          <t>134217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246807</t>
+          <t>246629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308189</t>
+          <t>307624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69722</t>
+          <t>69749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106684</t>
+          <t>106712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>58861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91983</t>
+          <t>94089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135616</t>
+          <t>136495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185385</t>
+          <t>186595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55808</t>
+          <t>56193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86811</t>
+          <t>86685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58592</t>
+          <t>58415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89233</t>
+          <t>87810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>124218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168511</t>
+          <t>164646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86475</t>
+          <t>84772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>37587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63167</t>
+          <t>62763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96373</t>
+          <t>95729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136522</t>
+          <t>136477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83629</t>
+          <t>82632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119226</t>
+          <t>118661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63301</t>
+          <t>63887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94689</t>
+          <t>94097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>155314</t>
+          <t>156773</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>202195</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50689</t>
+          <t>51595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82454</t>
+          <t>81573</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71258</t>
+          <t>73368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103034</t>
+          <t>103803</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142513</t>
+          <t>145562</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>34454</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60817</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67825</t>
+          <t>65136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80994</t>
+          <t>78973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117012</t>
+          <t>116162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>326038</t>
+          <t>326159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>390894</t>
+          <t>392089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205107</t>
+          <t>206351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260080</t>
+          <t>261174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>541774</t>
+          <t>545721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>630682</t>
+          <t>638147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242903</t>
+          <t>240086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>302861</t>
+          <t>304088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181719</t>
+          <t>180301</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>232862</t>
+          <t>231953</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>438347</t>
+          <t>437111</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>519736</t>
+          <t>516733</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>370476</t>
+          <t>369026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>439382</t>
+          <t>438657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>253179</t>
+          <t>250055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>309933</t>
+          <t>309713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>643231</t>
+          <t>643105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>731496</t>
+          <t>729841</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>212785</t>
+          <t>213329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>268033</t>
+          <t>268936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>157907</t>
+          <t>157621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208028</t>
+          <t>207231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>384830</t>
+          <t>384070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>458538</t>
+          <t>457579</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122521</t>
+          <t>122703</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>173355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112331</t>
+          <t>112779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156531</t>
+          <t>156305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246885</t>
+          <t>247280</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>314267</t>
+          <t>312456</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>825</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>825</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>323046</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141962</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>459402</t>
+          <t>104703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>68646</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55490</t>
+          <t>67372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81365</t>
+          <t>95192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>391692</t>
+          <t>164272</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207583</t>
+          <t>141858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>587591</t>
+          <t>186423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>62403</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111085</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29776</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>54140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>92078</t>
+          <t>106156</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38420</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146716</t>
+          <t>128150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>86496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163030</t>
+          <t>104477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76517</t>
+          <t>80706</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>67589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>95533</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>155700</t>
+          <t>167202</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70419</t>
+          <t>147433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241851</t>
+          <t>192754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82533</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>42976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67565</t>
+          <t>78027</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>62364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107189</t>
+          <t>96287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27716</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>52564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>40905</t>
+          <t>44320</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53915</t>
+          <t>57822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34315</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75220</t>
+          <t>80614</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>95641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>30567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35159</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>28344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>50875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>40610</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25152</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>38832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>59685</t>
+          <t>69355</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47896</t>
+          <t>55739</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72615</t>
+          <t>84126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28396</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>21193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45689</t>
+          <t>51270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>373842</t>
+          <t>145412</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195463</t>
+          <t>122936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>552980</t>
+          <t>168603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>107384</t>
+          <t>122383</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>105482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123304</t>
+          <t>139000</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>481226</t>
+          <t>267795</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>299384</t>
+          <t>239070</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>761884</t>
+          <t>298069</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>83796</t>
+          <t>94254</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32880</t>
+          <t>76806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142476</t>
+          <t>116199</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>57487</t>
+          <t>64337</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47039</t>
+          <t>52754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>70512</t>
+          <t>78708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>141284</t>
+          <t>158591</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62942</t>
+          <t>137050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>194960</t>
+          <t>183569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>119038</t>
+          <t>134138</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>112269</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196030</t>
+          <t>155631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>110688</t>
+          <t>120311</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95994</t>
+          <t>104656</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125218</t>
+          <t>136209</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>229726</t>
+          <t>254450</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108501</t>
+          <t>228174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>311070</t>
+          <t>284982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>62531</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93688</t>
+          <t>81328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>41933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>67803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>103597</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>99597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143739</t>
+          <t>139146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66130</t>
+          <t>60680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>43158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>75865</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30752</t>
+          <t>59976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99306</t>
+          <t>96598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
